--- a/aggregated_refactorings.xlsx
+++ b/aggregated_refactorings.xlsx
@@ -213,16 +213,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultColWidth="8.55078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="49.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.8"/>
@@ -683,6 +683,10 @@
       <c r="J14" s="2" t="n">
         <f aca="false">SUM(J2:J13)</f>
         <v>2</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <f aca="false">SUM(B14:J14)</f>
+        <v>453</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
